--- a/sheets/대금율보/검수/잦은뱃노래.xlsx
+++ b/sheets/대금율보/검수/잦은뱃노래.xlsx
@@ -4070,7 +4070,7 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -4124,7 +4124,7 @@
       <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -4149,7 +4149,7 @@
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -4183,7 +4183,7 @@
       <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -4383,7 +4383,7 @@
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -4404,16 +4404,12 @@
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="23"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -4660,16 +4656,12 @@
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H12" s="21"/>
       <c r="I12" s="23"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -4715,7 +4707,7 @@
       <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–‹
+–
 湳</t>
         </is>
       </c>
@@ -4930,7 +4922,7 @@
       <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -4997,7 +4989,7 @@
       <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–‹
+–
 湳</t>
         </is>
       </c>
@@ -5009,7 +5001,7 @@
       <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/잦은뱃노래.xlsx
+++ b/sheets/대금율보/검수/잦은뱃노래.xlsx
@@ -4007,30 +4007,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="11.63" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="11.63" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="11.63" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="11.63" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       <c r="R6" s="21"/>
       <c r="S6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="S10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
       <c r="R15" s="21"/>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5015,7 +5015,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -5120,6 +5120,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>